--- a/MK_UNet_ColonDB_Results/All_Runs_Summary_Polyp.xlsx
+++ b/MK_UNet_ColonDB_Results/All_Runs_Summary_Polyp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study Material\✅✅Professor_Mail\Mostafijur_Rahman\MK_UNet_ColonDB_Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study Material\✅✅Professor_Mail\Mostafijur_Rahman\MK-UNet\MK_UNet_ColonDB_Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D62F847-2FBC-4615-9C6F-C7179C26EEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EFE288-FF63-42FA-A1D7-E0C74B03F304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-10095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -481,7 +481,7 @@
         <v>0.86713664704247528</v>
       </c>
       <c r="F2">
-        <v>0.79278272272724859</v>
+        <v>0.79278272272724004</v>
       </c>
       <c r="G2">
         <v>0.89377105263157908</v>
